--- a/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt2_rubricas.xlsx
@@ -1608,13 +1608,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDEEF966-9E0B-4DA6-B47C-793DA1A0F617}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9877B47-D657-4F67-AD32-2544B6A73552}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42C3E29F-41E2-4CF1-8AE0-2F66B618E4DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECF2C7EE-75D6-4890-87E7-BAB4CD58851F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA33A5FC-AA36-4E56-9958-BD3EFCCB4794}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9E1524B-89DC-4C61-84ED-F9A3D9AE8718}"/>
 </file>